--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/29.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/29.xlsx
@@ -426,13 +426,13 @@
         <v>-15.4673277915437</v>
       </c>
       <c r="E2">
-        <v>-24.83703364424072</v>
+        <v>-14.12943873920813</v>
       </c>
       <c r="F2">
-        <v>-3.257507129878701</v>
+        <v>-0.7789281869201941</v>
       </c>
       <c r="G2">
-        <v>-17.88425343673791</v>
+        <v>-14.05837513664162</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-15.09183882618377</v>
       </c>
       <c r="E3">
-        <v>-25.64769389024982</v>
+        <v>-14.3476251453717</v>
       </c>
       <c r="F3">
-        <v>-2.797809564921839</v>
+        <v>-0.8534874777131678</v>
       </c>
       <c r="G3">
-        <v>-17.36555054055383</v>
+        <v>-12.8972310836521</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-14.65978150973517</v>
       </c>
       <c r="E4">
-        <v>-25.93714036339809</v>
+        <v>-13.06981204920533</v>
       </c>
       <c r="F4">
-        <v>-3.09042615579984</v>
+        <v>-0.8472943957308419</v>
       </c>
       <c r="G4">
-        <v>-17.17184555523276</v>
+        <v>-13.21071988294785</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-14.19174092867767</v>
       </c>
       <c r="E5">
-        <v>-26.48050290263044</v>
+        <v>-15.22114966755528</v>
       </c>
       <c r="F5">
-        <v>-2.964355246401282</v>
+        <v>-1.429773512899893</v>
       </c>
       <c r="G5">
-        <v>-17.45683717852646</v>
+        <v>-13.3976167313674</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-13.68375183167472</v>
       </c>
       <c r="E6">
-        <v>-26.36932433726813</v>
+        <v>-15.91679573071757</v>
       </c>
       <c r="F6">
-        <v>-3.016289714486288</v>
+        <v>-0.639617496068563</v>
       </c>
       <c r="G6">
-        <v>-17.34163184903259</v>
+        <v>-12.92082865225603</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-13.13983398050777</v>
       </c>
       <c r="E7">
-        <v>-27.33111787480922</v>
+        <v>-15.63629752220846</v>
       </c>
       <c r="F7">
-        <v>-2.918404019264807</v>
+        <v>-0.5580320939817421</v>
       </c>
       <c r="G7">
-        <v>-16.94291139955554</v>
+        <v>-11.53392194621591</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.57821841360055</v>
       </c>
       <c r="E8">
-        <v>-27.88764468798187</v>
+        <v>-18.30728206141259</v>
       </c>
       <c r="F8">
-        <v>-3.02349478454858</v>
+        <v>-0.5415908510206076</v>
       </c>
       <c r="G8">
-        <v>-16.87422254543397</v>
+        <v>-10.86518512619206</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-12.01572064110741</v>
       </c>
       <c r="E9">
-        <v>-27.44243229439176</v>
+        <v>-19.21190361460684</v>
       </c>
       <c r="F9">
-        <v>-3.039213065759316</v>
+        <v>-0.6656053182879667</v>
       </c>
       <c r="G9">
-        <v>-16.0159156114676</v>
+        <v>-11.73612344666352</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.48306775067483</v>
       </c>
       <c r="E10">
-        <v>-28.83375159156039</v>
+        <v>-18.86393114338344</v>
       </c>
       <c r="F10">
-        <v>-2.863657681326938</v>
+        <v>-0.7930421740385903</v>
       </c>
       <c r="G10">
-        <v>-15.62393212216296</v>
+        <v>-10.66761176840835</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.99707298960832</v>
       </c>
       <c r="E11">
-        <v>-29.00950166779807</v>
+        <v>-17.68352099464806</v>
       </c>
       <c r="F11">
-        <v>-2.789259136684382</v>
+        <v>-0.4903278742437481</v>
       </c>
       <c r="G11">
-        <v>-15.25943112665259</v>
+        <v>-8.932511814184311</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.57961566886885</v>
       </c>
       <c r="E12">
-        <v>-29.7997520814546</v>
+        <v>-18.69745991038747</v>
       </c>
       <c r="F12">
-        <v>-2.841880933136688</v>
+        <v>-0.81853825557125</v>
       </c>
       <c r="G12">
-        <v>-15.78339447969858</v>
+        <v>-9.513598630510426</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-10.22974807178164</v>
       </c>
       <c r="E13">
-        <v>-30.43395580928082</v>
+        <v>-21.98287233142633</v>
       </c>
       <c r="F13">
-        <v>-2.698091521956195</v>
+        <v>-0.7263420238509849</v>
       </c>
       <c r="G13">
-        <v>-14.59466696127585</v>
+        <v>-9.300204175594544</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.948502954130268</v>
       </c>
       <c r="E14">
-        <v>-30.87851836685083</v>
+        <v>-21.64865283576422</v>
       </c>
       <c r="F14">
-        <v>-2.531396180267742</v>
+        <v>-0.991334032445975</v>
       </c>
       <c r="G14">
-        <v>-14.32432781253897</v>
+        <v>-8.771165756236853</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-9.715290822072333</v>
       </c>
       <c r="E15">
-        <v>-31.00680324277711</v>
+        <v>-22.63582847011831</v>
       </c>
       <c r="F15">
-        <v>-2.496545147892582</v>
+        <v>-0.5398376885722161</v>
       </c>
       <c r="G15">
-        <v>-14.03529897896013</v>
+        <v>-6.930859975320313</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-9.509694581556491</v>
       </c>
       <c r="E16">
-        <v>-31.48392779269927</v>
+        <v>-25.02137423567096</v>
       </c>
       <c r="F16">
-        <v>-2.257683495049385</v>
+        <v>-0.1149103869888271</v>
       </c>
       <c r="G16">
-        <v>-13.9512789884462</v>
+        <v>-6.764889085254492</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-9.305213692468154</v>
       </c>
       <c r="E17">
-        <v>-32.71479419882812</v>
+        <v>-23.93257964458475</v>
       </c>
       <c r="F17">
-        <v>-2.19066026885503</v>
+        <v>-0.09598193388749481</v>
       </c>
       <c r="G17">
-        <v>-12.89418538175597</v>
+        <v>-5.869482522702274</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.081744904303639</v>
       </c>
       <c r="E18">
-        <v>-33.62764398929431</v>
+        <v>-24.81338142449866</v>
       </c>
       <c r="F18">
-        <v>-2.254959520874829</v>
+        <v>0.50860967712588</v>
       </c>
       <c r="G18">
-        <v>-12.97311209795774</v>
+        <v>-4.984490936416604</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-8.826326072370241</v>
       </c>
       <c r="E19">
-        <v>-34.26093522960798</v>
+        <v>-25.17566387358629</v>
       </c>
       <c r="F19">
-        <v>-2.248330127912799</v>
+        <v>-0.2426782372757777</v>
       </c>
       <c r="G19">
-        <v>-12.83033820048559</v>
+        <v>-6.643405306145396</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-8.5310220755379</v>
       </c>
       <c r="E20">
-        <v>-34.16362964436816</v>
+        <v>-26.41378489507543</v>
       </c>
       <c r="F20">
-        <v>-1.972605344328876</v>
+        <v>0.1009677337565549</v>
       </c>
       <c r="G20">
-        <v>-12.43709504860326</v>
+        <v>-4.12304726055177</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-8.196933568651101</v>
       </c>
       <c r="E21">
-        <v>-34.52905032594312</v>
+        <v>-26.8137533048549</v>
       </c>
       <c r="F21">
-        <v>-1.827145123407594</v>
+        <v>0.7861565143655164</v>
       </c>
       <c r="G21">
-        <v>-12.75535765456664</v>
+        <v>-5.048516887146109</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-7.824575974296208</v>
       </c>
       <c r="E22">
-        <v>-35.44101479974081</v>
+        <v>-27.21532932290709</v>
       </c>
       <c r="F22">
-        <v>-1.582477604678396</v>
+        <v>0.4548381101789645</v>
       </c>
       <c r="G22">
-        <v>-11.96647782637709</v>
+        <v>-5.360419935128544</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-7.428368774331083</v>
       </c>
       <c r="E23">
-        <v>-35.69431272912285</v>
+        <v>-27.74270634889237</v>
       </c>
       <c r="F23">
-        <v>-1.665908024156704</v>
+        <v>0.8282577524215586</v>
       </c>
       <c r="G23">
-        <v>-11.98789374547063</v>
+        <v>-5.75376240337705</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-7.020518845304826</v>
       </c>
       <c r="E24">
-        <v>-37.23912465278146</v>
+        <v>-28.18021580819542</v>
       </c>
       <c r="F24">
-        <v>-1.68666169832558</v>
+        <v>1.039172538827953</v>
       </c>
       <c r="G24">
-        <v>-12.13368023938352</v>
+        <v>-4.82597870545076</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-6.624182796646647</v>
       </c>
       <c r="E25">
-        <v>-36.93783169162913</v>
+        <v>-27.14135217151779</v>
       </c>
       <c r="F25">
-        <v>-1.07238335008042</v>
+        <v>1.322898204696677</v>
       </c>
       <c r="G25">
-        <v>-11.92426506020584</v>
+        <v>-4.469184659955808</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-6.254513464464769</v>
       </c>
       <c r="E26">
-        <v>-36.56257742874652</v>
+        <v>-28.20093357678051</v>
       </c>
       <c r="F26">
-        <v>-1.154813659273128</v>
+        <v>1.103751314941828</v>
       </c>
       <c r="G26">
-        <v>-11.64227610171626</v>
+        <v>-4.711675499616344</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.932408176090806</v>
       </c>
       <c r="E27">
-        <v>-36.51945050653447</v>
+        <v>-27.21983968301873</v>
       </c>
       <c r="F27">
-        <v>-1.505268773888892</v>
+        <v>1.57525224008646</v>
       </c>
       <c r="G27">
-        <v>-12.40145702587301</v>
+        <v>-4.673743268827375</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.66688899103946</v>
       </c>
       <c r="E28">
-        <v>-36.64717838015782</v>
+        <v>-28.77584599442431</v>
       </c>
       <c r="F28">
-        <v>-1.092416438057771</v>
+        <v>1.315804785901423</v>
       </c>
       <c r="G28">
-        <v>-11.87030647846126</v>
+        <v>-5.656323116519681</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.470929334411455</v>
       </c>
       <c r="E29">
-        <v>-35.87822311552235</v>
+        <v>-29.21759863387255</v>
       </c>
       <c r="F29">
-        <v>-1.1416760268516</v>
+        <v>0.7602169951765336</v>
       </c>
       <c r="G29">
-        <v>-11.89252686012085</v>
+        <v>-4.434036597965366</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.344840832418596</v>
       </c>
       <c r="E30">
-        <v>-35.5489894697427</v>
+        <v>-27.62413278547553</v>
       </c>
       <c r="F30">
-        <v>-1.258366646113009</v>
+        <v>1.157426275827901</v>
       </c>
       <c r="G30">
-        <v>-11.82250882196526</v>
+        <v>-5.307802124327368</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.290325958119943</v>
       </c>
       <c r="E31">
-        <v>-36.06019757928359</v>
+        <v>-27.90722580959103</v>
       </c>
       <c r="F31">
-        <v>-1.385506557004488</v>
+        <v>0.818150541269224</v>
       </c>
       <c r="G31">
-        <v>-12.4021985880738</v>
+        <v>-5.728413556182851</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.298503791024464</v>
       </c>
       <c r="E32">
-        <v>-36.13201691280823</v>
+        <v>-26.96403071479944</v>
       </c>
       <c r="F32">
-        <v>-1.372433856525493</v>
+        <v>0.9383728247220634</v>
       </c>
       <c r="G32">
-        <v>-11.59171745024051</v>
+        <v>-4.620956620203696</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.360614789417602</v>
       </c>
       <c r="E33">
-        <v>-35.11264835673362</v>
+        <v>-27.5360901938184</v>
       </c>
       <c r="F33">
-        <v>-1.132762138106548</v>
+        <v>1.123189721347932</v>
       </c>
       <c r="G33">
-        <v>-12.82644499893141</v>
+        <v>-4.55565941998711</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.461686601730768</v>
       </c>
       <c r="E34">
-        <v>-35.06942633656741</v>
+        <v>-27.55560791679146</v>
       </c>
       <c r="F34">
-        <v>-1.1701304710343</v>
+        <v>0.7511106861627569</v>
       </c>
       <c r="G34">
-        <v>-12.67920186498124</v>
+        <v>-6.017463908307696</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.585899475316427</v>
       </c>
       <c r="E35">
-        <v>-34.56820804068744</v>
+        <v>-26.44863603103846</v>
       </c>
       <c r="F35">
-        <v>-1.129312034769764</v>
+        <v>0.9108480159117258</v>
       </c>
       <c r="G35">
-        <v>-12.88208533780994</v>
+        <v>-4.159456640392674</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.718888507681527</v>
       </c>
       <c r="E36">
-        <v>-34.54387654984423</v>
+        <v>-26.28256783222918</v>
       </c>
       <c r="F36">
-        <v>-1.419161891413491</v>
+        <v>0.9561087472690698</v>
       </c>
       <c r="G36">
-        <v>-12.78844324668611</v>
+        <v>-6.347902700764511</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.846576933518072</v>
       </c>
       <c r="E37">
-        <v>-33.94848184426375</v>
+        <v>-26.46329470140129</v>
       </c>
       <c r="F37">
-        <v>-1.353447598158247</v>
+        <v>0.7329883393723833</v>
       </c>
       <c r="G37">
-        <v>-12.70540152237903</v>
+        <v>-4.614150138574954</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.961326029594188</v>
       </c>
       <c r="E38">
-        <v>-33.34380376696754</v>
+        <v>-26.8291048317409</v>
       </c>
       <c r="F38">
-        <v>-1.250753771777491</v>
+        <v>1.540013199762017</v>
       </c>
       <c r="G38">
-        <v>-12.58657942188351</v>
+        <v>-5.611518193191185</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.054688542712993</v>
       </c>
       <c r="E39">
-        <v>-33.00862649905282</v>
+        <v>-25.75780826422033</v>
       </c>
       <c r="F39">
-        <v>-1.518202900100286</v>
+        <v>0.7695877830781889</v>
       </c>
       <c r="G39">
-        <v>-12.7538116297998</v>
+        <v>-5.353682974956127</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.127312638776669</v>
       </c>
       <c r="E40">
-        <v>-32.71142048569241</v>
+        <v>-24.62305419043028</v>
       </c>
       <c r="F40">
-        <v>-1.117651208114383</v>
+        <v>0.9002973671030682</v>
       </c>
       <c r="G40">
-        <v>-12.97176139537772</v>
+        <v>-5.420920154858725</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.178313431657235</v>
       </c>
       <c r="E41">
-        <v>-32.51020227163558</v>
+        <v>-24.64704151724891</v>
       </c>
       <c r="F41">
-        <v>-1.537787799303568</v>
+        <v>1.657036397265669</v>
       </c>
       <c r="G41">
-        <v>-13.13033983725435</v>
+        <v>-5.560701319163372</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.216337155146896</v>
       </c>
       <c r="E42">
-        <v>-31.79294180203468</v>
+        <v>-23.37693135536959</v>
       </c>
       <c r="F42">
-        <v>-1.259273317749598</v>
+        <v>1.185882303716517</v>
       </c>
       <c r="G42">
-        <v>-13.06151028494736</v>
+        <v>-6.107163139694249</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.246375596284142</v>
       </c>
       <c r="E43">
-        <v>-31.15017020138595</v>
+        <v>-22.36937305950698</v>
       </c>
       <c r="F43">
-        <v>-1.191406768155271</v>
+        <v>1.419450419537358</v>
       </c>
       <c r="G43">
-        <v>-13.15732409394494</v>
+        <v>-5.642362545980574</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.279837008368379</v>
       </c>
       <c r="E44">
-        <v>-30.40321199924275</v>
+        <v>-22.15024925922383</v>
       </c>
       <c r="F44">
-        <v>-1.102843557805024</v>
+        <v>1.390847106998606</v>
       </c>
       <c r="G44">
-        <v>-13.46418849161661</v>
+        <v>-5.962383051625302</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.322847822763306</v>
       </c>
       <c r="E45">
-        <v>-29.24325696760001</v>
+        <v>-22.2319429303222</v>
       </c>
       <c r="F45">
-        <v>-1.297324227926904</v>
+        <v>1.819930052904108</v>
       </c>
       <c r="G45">
-        <v>-13.20927648509273</v>
+        <v>-6.612203414437765</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.38580543980485</v>
       </c>
       <c r="E46">
-        <v>-29.82617572728936</v>
+        <v>-22.60320534336705</v>
       </c>
       <c r="F46">
-        <v>-1.19748423960577</v>
+        <v>1.606086994260066</v>
       </c>
       <c r="G46">
-        <v>-12.80878654902493</v>
+        <v>-7.001821518954591</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.472952664093691</v>
       </c>
       <c r="E47">
-        <v>-29.3586741846335</v>
+        <v>-19.80849383732535</v>
       </c>
       <c r="F47">
-        <v>-1.226229293823954</v>
+        <v>1.045814601437306</v>
       </c>
       <c r="G47">
-        <v>-13.09833348298067</v>
+        <v>-5.471876071799187</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.590892707495152</v>
       </c>
       <c r="E48">
-        <v>-30.03326963637114</v>
+        <v>-20.27731769439145</v>
       </c>
       <c r="F48">
-        <v>-1.08572844797687</v>
+        <v>1.093129399366975</v>
       </c>
       <c r="G48">
-        <v>-13.60802010838855</v>
+        <v>-5.561287285723822</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.742079411744496</v>
       </c>
       <c r="E49">
-        <v>-28.44639951036629</v>
+        <v>-19.86468767128653</v>
       </c>
       <c r="F49">
-        <v>-1.133339398912726</v>
+        <v>1.54220346504307</v>
       </c>
       <c r="G49">
-        <v>-13.68920296137533</v>
+        <v>-5.897655265241472</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.928438324533899</v>
       </c>
       <c r="E50">
-        <v>-27.77364488331277</v>
+        <v>-17.12244759357171</v>
       </c>
       <c r="F50">
-        <v>-1.249648345048515</v>
+        <v>0.9069758549484763</v>
       </c>
       <c r="G50">
-        <v>-13.5599476766128</v>
+        <v>-6.29048790947693</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.150108055357872</v>
       </c>
       <c r="E51">
-        <v>-28.22898747325803</v>
+        <v>-18.81280920031085</v>
       </c>
       <c r="F51">
-        <v>-1.158496567379482</v>
+        <v>1.815082329096948</v>
       </c>
       <c r="G51">
-        <v>-13.70701369637661</v>
+        <v>-5.220344132270901</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.403620105761631</v>
       </c>
       <c r="E52">
-        <v>-26.54450835425485</v>
+        <v>-18.28431816971969</v>
       </c>
       <c r="F52">
-        <v>-1.126835118718016</v>
+        <v>1.493571023791755</v>
       </c>
       <c r="G52">
-        <v>-13.85645999838316</v>
+        <v>-6.41440493955739</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.687530203016882</v>
       </c>
       <c r="E53">
-        <v>-27.03151856293575</v>
+        <v>-15.45629973735157</v>
       </c>
       <c r="F53">
-        <v>-1.247150840819867</v>
+        <v>1.772393536146278</v>
       </c>
       <c r="G53">
-        <v>-14.49827711735443</v>
+        <v>-6.418205445836473</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.993426255183711</v>
       </c>
       <c r="E54">
-        <v>-26.16398974033833</v>
+        <v>-17.89327991068335</v>
       </c>
       <c r="F54">
-        <v>-1.2663358542795</v>
+        <v>1.612223854682394</v>
       </c>
       <c r="G54">
-        <v>-13.86463208004685</v>
+        <v>-7.051506186407972</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.319740195698511</v>
       </c>
       <c r="E55">
-        <v>-26.43297203944593</v>
+        <v>-17.22856785346745</v>
       </c>
       <c r="F55">
-        <v>-1.180727047314505</v>
+        <v>1.654697263628564</v>
       </c>
       <c r="G55">
-        <v>-13.84276261621443</v>
+        <v>-6.046844999968727</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.654484488216935</v>
       </c>
       <c r="E56">
-        <v>-26.02164168838122</v>
+        <v>-16.75039722604953</v>
       </c>
       <c r="F56">
-        <v>-1.400982531210162</v>
+        <v>1.072249820577822</v>
       </c>
       <c r="G56">
-        <v>-13.65500502595466</v>
+        <v>-6.426144134039646</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.995324459722164</v>
       </c>
       <c r="E57">
-        <v>-25.02799486467017</v>
+        <v>-16.41817478742481</v>
       </c>
       <c r="F57">
-        <v>-1.063293669978755</v>
+        <v>1.590051971866242</v>
       </c>
       <c r="G57">
-        <v>-14.16518326737513</v>
+        <v>-6.733074742622096</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.330670868769616</v>
       </c>
       <c r="E58">
-        <v>-25.37767004212045</v>
+        <v>-16.64715707562266</v>
       </c>
       <c r="F58">
-        <v>-1.247771653538719</v>
+        <v>1.551015204756575</v>
       </c>
       <c r="G58">
-        <v>-14.34280396719364</v>
+        <v>-7.569702569124552</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.660525659477111</v>
       </c>
       <c r="E59">
-        <v>-25.05916887973897</v>
+        <v>-15.05604150523562</v>
       </c>
       <c r="F59">
-        <v>-1.228649196462745</v>
+        <v>1.353805809342393</v>
       </c>
       <c r="G59">
-        <v>-14.38347236387082</v>
+        <v>-7.013673271985182</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.975575720191316</v>
       </c>
       <c r="E60">
-        <v>-24.81471279585691</v>
+        <v>-14.60504625033772</v>
       </c>
       <c r="F60">
-        <v>-1.622230206861841</v>
+        <v>1.093251344722464</v>
       </c>
       <c r="G60">
-        <v>-14.88584268363691</v>
+        <v>-7.75631802117327</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-10.27812884914861</v>
       </c>
       <c r="E61">
-        <v>-24.39319337827494</v>
+        <v>-14.61038532119276</v>
       </c>
       <c r="F61">
-        <v>-1.591951333464555</v>
+        <v>1.051639471794293</v>
       </c>
       <c r="G61">
-        <v>-14.47267335815371</v>
+        <v>-7.045401540433557</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-10.56118956669882</v>
       </c>
       <c r="E62">
-        <v>-23.88288869929858</v>
+        <v>-14.13835077605522</v>
       </c>
       <c r="F62">
-        <v>-1.604662948994829</v>
+        <v>1.58406556350588</v>
       </c>
       <c r="G62">
-        <v>-14.93969532792424</v>
+        <v>-8.460404846465465</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.8284756160443</v>
       </c>
       <c r="E63">
-        <v>-22.7298124196735</v>
+        <v>-13.30475380919727</v>
       </c>
       <c r="F63">
-        <v>-1.493312586080282</v>
+        <v>1.265422349613548</v>
       </c>
       <c r="G63">
-        <v>-14.22549975182788</v>
+        <v>-8.565762958252771</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-11.07471274043074</v>
       </c>
       <c r="E64">
-        <v>-23.48133532361643</v>
+        <v>-13.99947153518799</v>
       </c>
       <c r="F64">
-        <v>-1.605978216757602</v>
+        <v>1.237134194551969</v>
       </c>
       <c r="G64">
-        <v>-14.93341853358178</v>
+        <v>-8.929985867937848</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-11.30285080249464</v>
       </c>
       <c r="E65">
-        <v>-23.45851634309178</v>
+        <v>-13.41631729485024</v>
       </c>
       <c r="F65">
-        <v>-1.524839419738935</v>
+        <v>1.201923660934004</v>
       </c>
       <c r="G65">
-        <v>-14.74690405317201</v>
+        <v>-7.202457131362121</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-11.50748327155435</v>
       </c>
       <c r="E66">
-        <v>-23.47023603382363</v>
+        <v>-13.3348817467703</v>
       </c>
       <c r="F66">
-        <v>-1.617920151212973</v>
+        <v>1.372954397565971</v>
       </c>
       <c r="G66">
-        <v>-14.23817417542498</v>
+        <v>-8.273607314412089</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-11.69007425295385</v>
       </c>
       <c r="E67">
-        <v>-23.14958837476252</v>
+        <v>-14.04885001576763</v>
       </c>
       <c r="F67">
-        <v>-1.502029303438861</v>
+        <v>0.9654858699943868</v>
       </c>
       <c r="G67">
-        <v>-14.91500362401958</v>
+        <v>-8.815126490452833</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-11.84529703174332</v>
       </c>
       <c r="E68">
-        <v>-23.12219563549012</v>
+        <v>-13.19110722550078</v>
       </c>
       <c r="F68">
-        <v>-2.015078753275047</v>
+        <v>1.132042637415238</v>
       </c>
       <c r="G68">
-        <v>-14.56560202671382</v>
+        <v>-9.047400986579179</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-11.97320271367117</v>
       </c>
       <c r="E69">
-        <v>-23.46630078991096</v>
+        <v>-13.29200615486568</v>
       </c>
       <c r="F69">
-        <v>-1.971678876368344</v>
+        <v>0.5796238422271426</v>
       </c>
       <c r="G69">
-        <v>-14.28033066232205</v>
+        <v>-8.155440701933342</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-12.06905030887081</v>
       </c>
       <c r="E70">
-        <v>-22.97327676774788</v>
+        <v>-13.47108465949901</v>
       </c>
       <c r="F70">
-        <v>-1.965128668702087</v>
+        <v>0.4206435239057537</v>
       </c>
       <c r="G70">
-        <v>-14.67528205570265</v>
+        <v>-7.098376890152974</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-12.13219673381071</v>
       </c>
       <c r="E71">
-        <v>-23.18522293672887</v>
+        <v>-12.86561409925146</v>
       </c>
       <c r="F71">
-        <v>-1.777175242510691</v>
+        <v>0.537249414900687</v>
       </c>
       <c r="G71">
-        <v>-14.46251329389369</v>
+        <v>-7.661960852212962</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-12.16002083423384</v>
       </c>
       <c r="E72">
-        <v>-23.28097751962106</v>
+        <v>-13.54910120970315</v>
       </c>
       <c r="F72">
-        <v>-1.805709663842121</v>
+        <v>0.440015414663409</v>
       </c>
       <c r="G72">
-        <v>-14.63802021038538</v>
+        <v>-7.714681289925855</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-12.15275497796672</v>
       </c>
       <c r="E73">
-        <v>-23.57287389720748</v>
+        <v>-12.71642352306876</v>
       </c>
       <c r="F73">
-        <v>-2.029897489525814</v>
+        <v>0.6225850325952684</v>
       </c>
       <c r="G73">
-        <v>-14.03112272576234</v>
+        <v>-8.170559963411195</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-12.11129377946988</v>
       </c>
       <c r="E74">
-        <v>-24.24401638751426</v>
+        <v>-13.12141853899674</v>
       </c>
       <c r="F74">
-        <v>-2.132635659672201</v>
+        <v>-0.06371867697816239</v>
       </c>
       <c r="G74">
-        <v>-14.32875401192497</v>
+        <v>-7.571563095717623</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-12.03760290540959</v>
       </c>
       <c r="E75">
-        <v>-24.50715695515197</v>
+        <v>-13.77076548390461</v>
       </c>
       <c r="F75">
-        <v>-2.1392618852224</v>
+        <v>0.4932722771878067</v>
       </c>
       <c r="G75">
-        <v>-14.25520527695176</v>
+        <v>-7.125625990486715</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-11.93668505199021</v>
       </c>
       <c r="E76">
-        <v>-23.63173047388517</v>
+        <v>-12.83927196594884</v>
       </c>
       <c r="F76">
-        <v>-2.087886465325544</v>
+        <v>0.3885014204989524</v>
       </c>
       <c r="G76">
-        <v>-14.22270234084719</v>
+        <v>-7.14027515449799</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-11.81171483987119</v>
       </c>
       <c r="E77">
-        <v>-24.49567727354253</v>
+        <v>-13.73566075339715</v>
       </c>
       <c r="F77">
-        <v>-2.429032556570356</v>
+        <v>0.1670296504602383</v>
       </c>
       <c r="G77">
-        <v>-13.91417770458758</v>
+        <v>-6.952944624612791</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-11.67042115409631</v>
       </c>
       <c r="E78">
-        <v>-25.01081836275908</v>
+        <v>-13.67654605370102</v>
       </c>
       <c r="F78">
-        <v>-2.319626984519968</v>
+        <v>0.1228798888025751</v>
       </c>
       <c r="G78">
-        <v>-13.47129623288942</v>
+        <v>-7.971655766320703</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-11.51438880799303</v>
       </c>
       <c r="E79">
-        <v>-25.3064960161419</v>
+        <v>-14.60607874241147</v>
       </c>
       <c r="F79">
-        <v>-2.666482335589938</v>
+        <v>0.3972331830637277</v>
       </c>
       <c r="G79">
-        <v>-12.73158793759467</v>
+        <v>-8.129601893999331</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-11.35000362985599</v>
       </c>
       <c r="E80">
-        <v>-25.85610784950483</v>
+        <v>-14.6722805039296</v>
       </c>
       <c r="F80">
-        <v>-2.373324117288858</v>
+        <v>-0.02587602412873678</v>
       </c>
       <c r="G80">
-        <v>-13.26536374761906</v>
+        <v>-6.893414394725617</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-11.1758389193093</v>
       </c>
       <c r="E81">
-        <v>-26.57030707067655</v>
+        <v>-15.61249586282414</v>
       </c>
       <c r="F81">
-        <v>-2.428340477085309</v>
+        <v>-0.3968005377015561</v>
       </c>
       <c r="G81">
-        <v>-13.15219605890461</v>
+        <v>-6.353580286364361</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.99825965344771</v>
       </c>
       <c r="E82">
-        <v>-26.25510263737266</v>
+        <v>-16.49111491826635</v>
       </c>
       <c r="F82">
-        <v>-2.949953024806276</v>
+        <v>-0.2785262125247073</v>
       </c>
       <c r="G82">
-        <v>-12.12398365149899</v>
+        <v>-7.15313000282698</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-10.81428177619884</v>
       </c>
       <c r="E83">
-        <v>-26.64613636793499</v>
+        <v>-15.98942339685258</v>
       </c>
       <c r="F83">
-        <v>-2.468253033566214</v>
+        <v>-0.4481648716570037</v>
       </c>
       <c r="G83">
-        <v>-12.87334549758626</v>
+        <v>-6.740126204620743</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-10.62910173965285</v>
       </c>
       <c r="E84">
-        <v>-27.89568725781949</v>
+        <v>-17.27537868928474</v>
       </c>
       <c r="F84">
-        <v>-2.921266567706963</v>
+        <v>-0.167265328994382</v>
       </c>
       <c r="G84">
-        <v>-13.21992319954702</v>
+        <v>-5.392181309032312</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-10.43760939134928</v>
       </c>
       <c r="E85">
-        <v>-28.35414090940802</v>
+        <v>-18.27066934906057</v>
       </c>
       <c r="F85">
-        <v>-2.811689955417708</v>
+        <v>-0.0331515691042656</v>
       </c>
       <c r="G85">
-        <v>-12.67091556949645</v>
+        <v>-6.280887327413044</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-10.24479308067276</v>
       </c>
       <c r="E86">
-        <v>-28.55672219414115</v>
+        <v>-18.34557030914744</v>
       </c>
       <c r="F86">
-        <v>-2.822425105965515</v>
+        <v>-0.3552971486285922</v>
       </c>
       <c r="G86">
-        <v>-12.39926544472601</v>
+        <v>-5.673921976606446</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-10.04578720417869</v>
       </c>
       <c r="E87">
-        <v>-29.72318464293291</v>
+        <v>-19.032517173741</v>
       </c>
       <c r="F87">
-        <v>-3.016842427850777</v>
+        <v>-0.6703540604754118</v>
       </c>
       <c r="G87">
-        <v>-12.66732693813188</v>
+        <v>-5.380216997453386</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-9.846704940489751</v>
       </c>
       <c r="E88">
-        <v>-31.11840522045915</v>
+        <v>-21.63741316327718</v>
       </c>
       <c r="F88">
-        <v>-2.874226542753624</v>
+        <v>-0.7908107324037362</v>
       </c>
       <c r="G88">
-        <v>-12.07011445448397</v>
+        <v>-5.708484072036438</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-9.644233492309949</v>
       </c>
       <c r="E89">
-        <v>-31.74716572252814</v>
+        <v>-23.034750802402</v>
       </c>
       <c r="F89">
-        <v>-3.084954451861996</v>
+        <v>-0.2179391671706981</v>
       </c>
       <c r="G89">
-        <v>-11.871759807953</v>
+        <v>-5.590820662479661</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.444665996990029</v>
       </c>
       <c r="E90">
-        <v>-33.21080701383627</v>
+        <v>-23.13372060183964</v>
       </c>
       <c r="F90">
-        <v>-2.931822759486325</v>
+        <v>-0.2995071484924491</v>
       </c>
       <c r="G90">
-        <v>-12.28325399739333</v>
+        <v>-5.512036299736086</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-9.244671796711598</v>
       </c>
       <c r="E91">
-        <v>-34.30146733621364</v>
+        <v>-24.82233874608583</v>
       </c>
       <c r="F91">
-        <v>-3.289505116047198</v>
+        <v>-1.119812966688958</v>
       </c>
       <c r="G91">
-        <v>-11.69312277065393</v>
+        <v>-4.575820642321272</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.049893996554452</v>
       </c>
       <c r="E92">
-        <v>-36.26345813511787</v>
+        <v>-27.04426168879334</v>
       </c>
       <c r="F92">
-        <v>-3.273653803539564</v>
+        <v>-0.5206004128173731</v>
       </c>
       <c r="G92">
-        <v>-11.67731491570391</v>
+        <v>-5.354517232432023</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-8.858472629733233</v>
       </c>
       <c r="E93">
-        <v>-36.87586858178217</v>
+        <v>-28.5806597077457</v>
       </c>
       <c r="F93">
-        <v>-3.386571243457439</v>
+        <v>-1.241575404144562</v>
       </c>
       <c r="G93">
-        <v>-11.75000456410968</v>
+        <v>-3.701767098497354</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-8.675106059832288</v>
       </c>
       <c r="E94">
-        <v>-38.0482112540729</v>
+        <v>-31.12811426873159</v>
       </c>
       <c r="F94">
-        <v>-3.63708580442644</v>
+        <v>-0.648545638166853</v>
       </c>
       <c r="G94">
-        <v>-11.56044603707655</v>
+        <v>-4.886055175351914</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-8.499821144328196</v>
       </c>
       <c r="E95">
-        <v>-39.7447474351215</v>
+        <v>-30.58838356565339</v>
       </c>
       <c r="F95">
-        <v>-3.390299287182383</v>
+        <v>-0.7481662832186982</v>
       </c>
       <c r="G95">
-        <v>-12.22490563226367</v>
+        <v>-5.413471427395365</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-8.333710106756039</v>
       </c>
       <c r="E96">
-        <v>-40.65946522111585</v>
+        <v>-32.93148620856915</v>
       </c>
       <c r="F96">
-        <v>-3.299054862717298</v>
+        <v>-0.5842408431763496</v>
       </c>
       <c r="G96">
-        <v>-12.08331028900351</v>
+        <v>-4.986262078280114</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.177692411531529</v>
       </c>
       <c r="E97">
-        <v>-41.93757040385572</v>
+        <v>-35.04211510982715</v>
       </c>
       <c r="F97">
-        <v>-3.698337214411975</v>
+        <v>-1.329429114244692</v>
       </c>
       <c r="G97">
-        <v>-12.07494454042577</v>
+        <v>-6.309222286683666</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-8.026122910743403</v>
       </c>
       <c r="E98">
-        <v>-44.89622625439711</v>
+        <v>-36.66657157009566</v>
       </c>
       <c r="F98">
-        <v>-3.933482701324594</v>
+        <v>-1.097619703842947</v>
       </c>
       <c r="G98">
-        <v>-12.82842139461835</v>
+        <v>-5.446398113328955</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.880097352343354</v>
       </c>
       <c r="E99">
-        <v>-46.14445935834537</v>
+        <v>-39.60160916445005</v>
       </c>
       <c r="F99">
-        <v>-3.836774491451242</v>
+        <v>-0.6787524529449872</v>
       </c>
       <c r="G99">
-        <v>-12.5200407670897</v>
+        <v>-4.998795803691795</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.724083585519703</v>
       </c>
       <c r="E100">
-        <v>-48.1647202965433</v>
+        <v>-40.45448384515866</v>
       </c>
       <c r="F100">
-        <v>-3.980746820664969</v>
+        <v>-1.58517782326422</v>
       </c>
       <c r="G100">
-        <v>-13.04839059297523</v>
+        <v>-5.386175979424073</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.56424237450091</v>
       </c>
       <c r="E101">
-        <v>-49.58816345620384</v>
+        <v>-43.86221714185569</v>
       </c>
       <c r="F101">
-        <v>-4.022680185893974</v>
+        <v>-1.532883062083452</v>
       </c>
       <c r="G101">
-        <v>-12.49729400868937</v>
+        <v>-5.266099182169168</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-7.372377987710174</v>
       </c>
       <c r="E102">
-        <v>-52.11403531006918</v>
+        <v>-45.50617321120124</v>
       </c>
       <c r="F102">
-        <v>-4.269530051374648</v>
+        <v>-1.760444973219988</v>
       </c>
       <c r="G102">
-        <v>-12.83841924214695</v>
+        <v>-5.534521525038816</v>
       </c>
     </row>
   </sheetData>
